--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0020.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0020.xlsx
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Gì?</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Haha, dễ thương quá! Phải nói là ta chưa thấy Zhezhi lo lắng như thế này kể từ khi cô ấy trở thành khách quen thân thiết của ta.</t>
+          <t>Haha, dễ thương quá! Phải nói là tao chưa thấy Zhezhi lo lắng như thế này kể từ khi cô ấy trở thành khách quen thân thiết của tao.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Họ mua cả đống quặng thừa—loại rẻ nhất—và dặn ta không được để ai biết họ lấy quặng ở đây.</t>
+          <t>Họ mua cả đống quặng thừa—loại rẻ nhất—và dặn tao không được để ai biết họ lấy quặng ở đây.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ta nhớ ngươi từng nói không đủ tiền mua màu vẽ đắt đỏ, nên tự làm lấy. Cái đó ám ảnh ta mãi.</t>
+          <t>Tao nhớ mày từng nói không đủ tiền mua màu vẽ đắt đỏ, nên tự làm lấy. Cái đó ám ảnh tao mãi.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Khi mấy gã đó đòi đồ thừa, ta đã đặc biệt chú ý.</t>
+          <t>Khi mấy gã đó đòi đồ thừa, tao đã đặc biệt chú ý.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Pfft, hóa ra lại là bọn trộm cắp, ăn cắp đồ của ta giữa đêm! Ta phát hiện ra, báo cho Đội Tuần Tra và thế là xong.</t>
+          <t>Pfft, hóa ra lại là bọn trộm cắp, ăn cắp đồ của tao giữa đêm! Tao phát hiện ra, báo cho Đội Tuần Tra và thế là xong.</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Có chuyện gì mà cậu lại đến đây? Lâu lắm rồi mới gặp lại! Trạm Tuần Tra dạo này bận rộn quá, chẳng có thời gian trò chuyện với cậu.</t>
+          <t>Có chuyện gì mà bạn lại đến đây? Lâu lắm rồi mới gặp lại! Trạm Tuần Tra dạo này bận rộn quá, chẳng có thời gian trò chuyện với cậu.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Sao tự dưng lại xin lỗi ta?</t>
+          <t>Sao tự dưng lại xin lỗi tao?</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Cứ thoải mái, ta sẽ ở đây nếu ngươi cần.</t>
+          <t>Cứ thoải mái, tao sẽ ở đây nếu mày cần.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Ta sẽ dốc hết sức, hứa luôn. Đi thôi nào.</t>
+          <t>Tao sẽ dốc hết sức, hứa luôn. Đi thôi nào.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Đợi đã! Ngươi giơ chân trái lên trước khi ta còn chưa nói hết câu... Không, không tính đâu. Làm lại nào.</t>
+          <t>Đợi đã! Mày giơ chân trái lên trước khi tao còn chưa nói hết câu... Không, không tính đâu. Làm lại nào.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Được rồi, nếu ngươi giơ chân phải lên, ta sẽ... để người khác xử lý vậy.</t>
+          <t>Được rồi, nếu mày giơ chân phải lên, tao sẽ... để người khác xử lý vậy.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Nhưng... ta, ừm, không ngờ... không ngờ lại có nhiều khán giả đến xem thế này...</t>
+          <t>Nhưng... tao, ừm, không ngờ... không ngờ lại có nhiều khán giả đến xem thế này...</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đầu ta... đau quá...</t>
+          <t>Đầu tao... đau quá...</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Ta nghe mấy câu kiểu như "Đừng cản ta!" "Ta... ta thắng rồi!" và "Ai mà chẳng muốn danh vọng với tiền tài!"</t>
+          <t>Tao nghe mấy câu kiểu như "Đừng cản tao!" "Tao... tao thắng rồi!" và "Ai mà chẳng muốn danh vọng với tiền tài!"</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Vậy là cô ấy đã ở đó cùng lúc với chúng ta... Mà ta thậm chí còn không nhận ra...</t>
+          <t>Vậy là cô ấy đã ở đó cùng lúc với chúng ta... Mà tao thậm chí còn không nhận ra...</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Ta nghĩ cô ấy muốn ta tiếp tục điều tra. Có lẽ câu chuyện này còn nhiều bí ẩn hơn ta tưởng...</t>
+          <t>Tao nghĩ cô ấy muốn tao tiếp tục điều tra. Có lẽ câu chuyện này còn nhiều bí ẩn hơn tao tưởng...</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tính cả ta.</t>
+          <t>Tính cả tao.</t>
         </is>
       </c>
     </row>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Ta nghĩ đúng là vậy. Cậu đi trước đi.</t>
+          <t>Tao nghĩ đúng là vậy. Cậu đi trước đi.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Ta không thể bỏ lỡ cơ hội ngon lành, nên hễ có là ta tích trữ ngay. Thường thì phải mất cả ngày mới vác hết mấy cái thùng về nhà, nhưng mà… đáng lắm!</t>
+          <t>Tao không thể bỏ lỡ cơ hội ngon lành, nên hễ có là tao tích trữ ngay. Thường thì phải mất cả ngày mới vác hết mấy cái thùng về nhà, nhưng mà… đáng lắm!</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Mua ba tặng một, mua năm tặng hai, chưa kể còn có phiếu giảm giá hàng tuần nữa—tất tần tật về khuyến mãi ta đều biết hết! Hê hê...</t>
+          <t>Mua ba tặng một, mua năm tặng hai, chưa kể còn có phiếu giảm giá hàng tuần nữa—tất tần tật về khuyến mãi tao đều biết hết! Hê hê...</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Mỗi khi thiên nhiên truyền cảm hứng mà lại hết giấy, ta thường phác họa đại khái lên quần áo mình.</t>
+          <t>Mỗi khi thiên nhiên truyền cảm hứng mà lại hết giấy, tao thường phác họa đại khái lên quần áo mình.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Ta vẽ đi vẽ lại, cố gắng cải thiện, nhưng dù có nỗ lực thế nào, vẫn cảm thấy chưa đủ tốt...</t>
+          <t>Tao vẽ đi vẽ lại, cố gắng cải thiện, nhưng dù có nỗ lực thế nào, vẫn cảm thấy chưa đủ tốt...</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>...Cậu chưa từng thấy ai pha chế thứ này trước đây à?</t>
+          <t>...Mày chưa từng thấy ai pha chế thứ này trước đây à?</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Gia đình lúc nào cũng mang thuốc và súp cho ta. Ta chưa bao giờ nghĩ chúng được làm ra sao...</t>
+          <t>Gia đình lúc nào cũng mang thuốc và súp cho tao. Tao chưa bao giờ nghĩ chúng được làm ra sao...</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Lâu lắm rồi ta không làm việc này. Giờ hơi gỉ sét rồi...</t>
+          <t>Lâu lắm rồi tao không làm việc này. Giờ hơi gỉ sét rồi...</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Nhà ta từng có một bể cá với đầy Gulpuff. Ta cứ tưởng đó là mốt thịnh hành...</t>
+          <t>Nhà tao từng có một bể cá với đầy Gulpuff. Tao cứ tưởng đó là mốt thịnh hành...</t>
         </is>
       </c>
     </row>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Ta xem qua và nhận ra những sắc tố này được làm thủ công từ những loại quặng đặc biệt này...</t>
+          <t>Tao xem qua và nhận ra những sắc tố này được làm thủ công từ những loại quặng đặc biệt này...</t>
         </is>
       </c>
     </row>
@@ -30929,7 +30929,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Ta đoán là cô ấy đang ngươi mò làm tác phẩm nghệ thuật mới, kiểu bí mật gì đó. Ta thấy cô ấy mạo hiểm vẽ vời ngoài hoang dã đấy.</t>
+          <t>Tao đoán là cô ấy đang mày mò làm tác phẩm nghệ thuật mới, kiểu bí mật gì đó. Tao thấy cô ấy mạo hiểm vẽ vời ngoài hoang dã đấy.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đúng rồi! Ta còn tận mắt thấy mấy bức tranh của cô ấy! Cố khuyên cô ấy đừng làm vậy, thế mà lại bị mắng. Nghệ sĩ mà, lúc nào cũng theo đuổi thứ gì đó kỳ lạ, phải không?</t>
+          <t>Đúng rồi! Tao còn tận mắt thấy mấy bức tranh của cô ấy! Cố khuyên cô ấy đừng làm vậy, thế mà lại bị mắng. Nghệ sĩ mà, lúc nào cũng theo đuổi thứ gì đó kỳ lạ, phải không?</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Tụi ta à? Cũng bình thường thôi. Đi săn tí, làm vài việc lặt vặt. Chỉ là cuộc sống thường nhật thôi mà.</t>
+          <t>Tụi tao à? Cũng bình thường thôi. Đi săn tí, làm vài việc lặt vặt. Chỉ là cuộc sống thường nhật thôi mà.</t>
         </is>
       </c>
     </row>
